--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/01_事故報告書.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/01_事故報告書.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +28,20 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -42,14 +54,8 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -62,26 +68,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,28 +101,61 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -484,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -504,191 +543,317 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>【速報義務】重大事故（死亡・骨折・誤嚥等）は24時間以内に行政へ速報。その後速やかに詳細報告書を提出。【保管】5年間</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>【事故基本情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>発生日時</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日（　曜日）　　時　　分頃</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日（　曜日）　　時　　分頃</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>発生場所</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>担当者氏名</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>利用者宅 / 事業所内 / 移動中 / 通院先 / その他（　　）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>担当者氏名・職種</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>当事者氏名（利用者）</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>当事者の障害種別</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>身体 ・ 精神 ・ 知的</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>年齢・性別</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　歳　男 / 女</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>障害種別・支援区分</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>当事者の状態（平時）</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>事故の種類</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>転倒 ・ 転落 ・ 誤薬 ・ 行方不明 ・ 医療事故 ・ その他（　　　　）</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>転倒 / 転落 / 誤薬 / 誤嚥・窒息 / 行方不明 / 暴力 / 熱傷 / 施設内感染 / 車両事故 / その他（　　）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>重症度</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>軽傷 ・ 中等症 ・ 重症 ・ 死亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>【事故の経緯・状況】（発生時の状況を時系列で具体的に記述してください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>例）10:30頃、訪問看護実施中に利用者が浴室内で転倒。右膝に擦り傷あり。本人は「足が滑った」と話していた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>【緊急対応の内容】（発見後の対応・連絡先・対応時刻）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>例）10:31 傷の確認・止血処置実施。10:35 管理者へ報告。10:40 主治医（〇〇クリニック）へ連絡・指示を受ける。10:45 家族へ報告・受診不要の判断。</t>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>軽傷 / 中等症 / 重症 / 死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>目撃者の有無・氏名</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（　　　　　　職種：　　　）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>救急搬送</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（搬送先：　　　　　　　）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>【原因分析】（なぜ起きたか。人・設備・環境・手順等の観点で）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>例）浴室マットの滑り止めが劣化していた。本人の下肢筋力低下があり、見守りが必要な状況だった。</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>【事故の経緯・状況（5W1H：いつ・どこで・誰が・何を・なぜ・どのように）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>例）〇時〇分、利用者宅浴室にて入浴介助中、担当ヘルパー山田が目を離した際に転倒した。右膝に擦り傷（約3cm）。本人は「足が滑った」と話している。浴室マットが端に寄っていた。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>【再発防止策】（具体的な対策と実施期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>例）①滑り止めマットを新品に交換（5/10まで）②訪問中の浴室使用時は必ず見守りを実施③スタッフへの周知徹底（5/9朝礼）</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>【緊急対応の内容（時系列で記録）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>例）〇時〇分：転倒確認・安全確認・出血部位の止血処置
+〇時〇分：管理者・サービス提供責任者へ電話報告
+〇時〇分：主治医（〇〇クリニック）へ連絡→自宅様子見の指示
+〇時〇分：家族（長男）へ電話報告・説明
+翌日：経過確認訪問実施</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>【行政への報告】</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>要　・　不要　／　報告先：　　　　　　　　報告日：　　年　　月　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>報告者氏名・日付：　　　　　　　　　　　　年　　月　　日</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>管理者確認・日付：　　　　　　　　　　　　年　　月　　日</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>【受診状況・診断結果】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>受診：なし / あり（受診日：　年　月　日　医療機関：　　　　　診断：　　　　　　治療内容：　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>【原因分析（なぜ起きたか：人・設備・環境・手順・ルール・体制の6観点で）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>①人的要因：担当者の注意不足 / 技術不足 / 疲労・健康問題
+②設備要件：浴室マットの劣化・ズレ / 手すりなし
+③環境要因：床が滑りやすい / 照明不十分
+④手順要因：見守り基準が曖昧
+⑤ルール要因：ヒヤリハット共有不足
+⑥体制要因：人手不足による急ぎの対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>【再発防止策（具体的な対策・実施担当者・実施期限を明記）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>①滑り止めマットを新品に交換（担当：〇〇　期限：〇月〇日）
+②浴室内では利用者から目を離さないよう手順書を改訂（担当：管理者　期限：〇月〇日）
+③スタッフ全員への朝礼での周知・注意喚起（担当：管理者　期限：〇月〇日）
+④1ヶ月後に再発防止策の効果確認を実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【行政への報告状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>速報：要 / 不要（報告先：　　　　　　　速報日：　年　月　日）
+詳細報告：提出予定日：　年　月　日　受理確認：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>【保険請求・補償対応】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>【フォローアップ実施記録】</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>①利用者・家族への経過報告日：　年　月　日（内容：　　　）
+②再発防止策の実施確認日：　年　月　日（内容：　　　）
+③全職員への周知・研修実施日：　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>報告者氏名・署名：　　　　　　　　　（報告日：　年　月　日）</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>管理者確認・署名：　　　　　　　　　（確認日：　年　月　日）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A9:H9"/>
+  <mergeCells count="44">
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E16:H16"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/01_事故報告書.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/01_事故報告書.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,40 +26,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFDC2626"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <sz val="9"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <i val="1"/>
-      <color rgb="FF6B7280"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,26 +74,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -96,68 +97,63 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
     </border>
     <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,9 +517,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -532,329 +528,487 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>事故報告書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【速報義務】重大事故（死亡・骨折・誤嚥等）は24時間以内に行政へ速報。その後速やかに詳細報告書を提出。【保管】5年間</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>【事故基本情報】</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+          <t>障害福祉サービス事業所 ／ 重大事故は発生後速やかに京都府・市町村・家族へ報告</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>1. 事故の概要</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>報告日</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>事業所名・サービス種別</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>利用者氏名</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>年齢・性別・障害支援区分</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>発生日時</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日（　曜日）　　時　　分頃</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>事業所名</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　年　　月　　日　　　時　　分頃</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>発生場所</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>利用者宅 / 事業所内 / 移動中 / 通院先 / その他（　　）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>担当者氏名・職種</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>当事者氏名（利用者）</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>年齢・性別</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　歳　男 / 女</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>障害種別・支援区分</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>当事者の状態（平時）</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>事故の種類</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>転倒 / 転落 / 誤薬 / 誤嚥・窒息 / 行方不明 / 暴力 / 熱傷 / 施設内感染 / 車両事故 / その他（　　）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>重症度</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>軽傷 / 中等症 / 重症 / 死亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>目撃者の有無・氏名</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>なし / あり（　　　　　　職種：　　　）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>救急搬送</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>なし / あり（搬送先：　　　　　　　）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>【事故の経緯・状況（5W1H：いつ・どこで・誰が・何を・なぜ・どのように）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>例）〇時〇分、利用者宅浴室にて入浴介助中、担当ヘルパー山田が目を離した際に転倒した。右膝に擦り傷（約3cm）。本人は「足が滑った」と話している。浴室マットが端に寄っていた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>【緊急対応の内容（時系列で記録）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>□事業所内　□利用者宅　□外出先　□送迎中　□その他（　　　）</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="8" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2. 事故の種類</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>例）〇時〇分：転倒確認・安全確認・出血部位の止血処置
-〇時〇分：管理者・サービス提供責任者へ電話報告
-〇時〇分：主治医（〇〇クリニック）へ連絡→自宅様子見の指示
-〇時〇分：家族（長男）へ電話報告・説明
-翌日：経過確認訪問実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>【受診状況・診断結果】</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>事故種別</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>□転倒・転落　□誤薬・与薬ミス　□誤嚥　□外傷　□無断外出　□自傷・他害　□交通事故　□その他</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>発見者</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>受診：なし / あり（受診日：　年　月　日　医療機関：　　　　　診断：　　　　　　治療内容：　　　　　）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>【原因分析（なぜ起きたか：人・設備・環境・手順・ルール・体制の6観点で）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>①人的要因：担当者の注意不足 / 技術不足 / 疲労・健康問題
-②設備要件：浴室マットの劣化・ズレ / 手すりなし
-③環境要因：床が滑りやすい / 照明不十分
-④手順要因：見守り基準が曖昧
-⑤ルール要因：ヒヤリハット共有不足
-⑥体制要因：人手不足による急ぎの対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>【再発防止策（具体的な対策・実施担当者・実施期限を明記）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>①滑り止めマットを新品に交換（担当：〇〇　期限：〇月〇日）
-②浴室内では利用者から目を離さないよう手順書を改訂（担当：管理者　期限：〇月〇日）
-③スタッフ全員への朝礼での周知・注意喚起（担当：管理者　期限：〇月〇日）
-④1ヶ月後に再発防止策の効果確認を実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>【行政への報告状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>速報：要 / 不要（報告先：　　　　　　　速報日：　年　月　日）
-詳細報告：提出予定日：　年　月　日　受理確認：</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>【保険請求・補償対応】</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>【フォローアップ実施記録】</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>発見の経緯</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>3. 事故の状況・対応（5W1Hで具体的に）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>（いつ・どこで・誰が・何を・なぜ・どのように。発生時の対応、受診の有無、家族への連絡時刻を記載）</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>4. 受診・治療</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>①利用者・家族への経過報告日：　年　月　日（内容：　　　）
-②再発防止策の実施確認日：　年　月　日（内容：　　　）
-③全職員への周知・研修実施日：　年　月　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>報告者氏名・署名：　　　　　　　　　（報告日：　年　月　日）</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>管理者確認・署名：　　　　　　　　　（確認日：　年　月　日）</t>
-        </is>
-      </c>
+          <t>受診の有無</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>□なし　□あり（医療機関：　　　　　　　　　／診断名：　　　　　　　　）</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>負傷の程度</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>□なし　□軽傷　□中等度　□重傷　□死亡</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>5. 原因分析・再発防止策</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>6. 報告先・確認</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>行政への報告</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>□京都府／市町村　報告日：　　月　　日　　　□報告不要（軽微）</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>家族への報告</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>□済（　　月　　日　　時）　□未</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>記入者 / 管理者確認</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>※ 重大事故（死亡・治療を要する負傷・無断外出等）は「障害福祉サービス事業者等における事故発生時の報告取扱要領」に基づき、
+　 市町村・京都府へ第一報（原則当日〜翌日）→後日詳細報告。虐待が疑われる場合は速やかに市町村虐待防止センターへ通報。</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="E25:H25"/>
+  <mergeCells count="39">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A18:H21"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="C7:H7"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A28:H31"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C34:H34"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C35:H35"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>